--- a/nursing/フォーマット/04_相談支援様式/03_サービス担当者会議記録.xlsx
+++ b/nursing/フォーマット/04_相談支援様式/03_サービス担当者会議記録.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="サービス担当者会議記録" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="担当者会議記録" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,40 +26,46 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FF0E7490"/>
-      <sz val="13"/>
+      <color rgb="00163A2B"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
+      <name val="Meiryo"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00163A2B"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="FF6B7280"/>
-      <sz val="9"/>
+      <name val="Meiryo"/>
+      <color rgb="00283129"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="005C665C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -68,21 +74,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFFAFE"/>
+        <fgColor rgb="00E4EFE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0E7490"/>
+        <fgColor rgb="001F4D3A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor rgb="00A9854A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6EDDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -91,44 +102,77 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <bottom style="medium">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DAD3C2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DAD3C2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DAD3C2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DAD3C2"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9854A"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9854A"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9854A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9854A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00A9854A"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -492,265 +536,331 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>サービス担当者会議記録（相談支援・計画相談用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
+          <t>サービス担当者会議 記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>開催日時</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　月　日（　曜日）　　時　　分〜　　時　　分</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>開催場所</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+          <t>計画案について本人・家族・サービス事業者等で検討。専門的見地からの意見を計画に反映</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>開催日時 / 場所</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>利用者氏名</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>（　　　）様</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>進行・記録者</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>【参加者一覧】</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>開催回数 / 目的</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>□新規　□更新　□区分変更　□状況変化</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>主催（相談支援専門員）</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="8" customHeight="1"/>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>出席者</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>所属・事業所</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>職種</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>所属機関</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>役割・職種</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>参加形態</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>山田 太郎</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>○○相談支援事業所</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>相談支援専門員（主任）</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>対面</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>佐藤 花子</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>○○就労継続支援事業所</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>サービス管理責任者</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>対面</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>田中 一郎</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>○○クリニック</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>精神科医</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>欠席（文書参加）</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>利用者本人</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>本人</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>対面</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>【検討事項①】個別支援計画・サービス等利用計画の目標の確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>各支援者から利用者の現在の状況・目標に向けた進捗を確認する。</t>
-        </is>
-      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>欠席時の意見聴取</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>【検討事項②】サービスの実施状況・課題の共有</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>各事業所から当月の支援状況・利用者の変化・課題を共有する。</t>
-        </is>
-      </c>
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>【検討事項③】計画の変更・調整事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="9" t="inlineStr"/>
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>【決定事項・次回の目標・役割分担】</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>次回会議の予定：　　年　月　日（　）　　時　　分〜</t>
-        </is>
-      </c>
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="8" customHeight="1"/>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>検討内容・各専門職からの意見</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="8" customHeight="1"/>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>会議の結論・計画への反映事項</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>記録者</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="6" t="inlineStr"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>※ 欠席者には事前・事後に意見照会し記録に残す。会議録は計画とともに保管（実地指導で確認）。</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
+  <mergeCells count="16">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>